--- a/Pruebas calificadas/COLEGIO DEBORA ARANGO DIAGNOSTICA 1104_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO DEBORA ARANGO DIAGNOSTICA 1104_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,11 +2048,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -2080,7 +2056,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -2333,7 +2305,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -2586,7 +2554,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2823,11 +2791,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -2835,7 +2799,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3076,11 +3040,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -3088,7 +3048,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3329,11 +3289,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -3341,7 +3297,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3582,11 +3538,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -3594,7 +3546,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3835,11 +3787,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -3847,7 +3795,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4088,11 +4036,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -4100,7 +4044,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4341,11 +4285,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -4353,7 +4293,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4594,11 +4534,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -4606,7 +4542,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4847,11 +4783,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -4859,7 +4791,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5096,11 +5028,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -5108,7 +5036,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5345,11 +5273,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -5357,7 +5281,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5598,11 +5522,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -5610,7 +5530,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5851,11 +5771,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -5863,7 +5779,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6104,11 +6020,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -6116,7 +6028,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6357,11 +6269,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -6369,7 +6277,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6610,11 +6518,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -6622,7 +6526,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6863,11 +6767,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -6875,7 +6775,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7116,11 +7016,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -7128,7 +7024,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7369,11 +7265,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -7381,7 +7273,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7622,11 +7514,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -7634,7 +7522,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7875,11 +7763,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -7887,7 +7771,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8128,11 +8012,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -8140,7 +8020,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8381,11 +8261,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -8393,7 +8269,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8634,11 +8510,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -8646,7 +8518,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8887,11 +8759,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -8899,7 +8767,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9140,11 +9008,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -9152,7 +9016,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9393,11 +9257,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -9405,7 +9265,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9646,11 +9506,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -9658,7 +9514,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9859,11 +9715,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -9871,7 +9723,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10096,11 +9948,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -10108,7 +9956,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10329,11 +10177,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -10341,7 +10185,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10550,11 +10394,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -10562,7 +10402,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10755,11 +10595,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -10767,7 +10603,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -10980,11 +10816,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -10992,7 +10824,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11193,11 +11025,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -11205,7 +11033,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11442,11 +11270,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -11454,7 +11278,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11695,11 +11519,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -11707,7 +11527,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -11944,11 +11764,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -11956,7 +11772,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12157,11 +11973,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -12169,7 +11981,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12410,11 +12222,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -12422,7 +12230,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12663,11 +12471,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -12675,7 +12479,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -12916,11 +12720,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -12928,7 +12728,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13169,11 +12969,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -13181,7 +12977,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13422,11 +13218,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -13434,7 +13226,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13675,11 +13467,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -13687,7 +13475,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -13928,11 +13716,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -13940,7 +13724,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14181,11 +13965,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -14193,7 +13973,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14434,11 +14214,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -14446,7 +14222,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14687,11 +14463,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -14699,7 +14471,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -14940,11 +14712,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -14952,7 +14720,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15193,11 +14961,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -15205,7 +14969,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15442,11 +15206,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -15454,7 +15214,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15695,11 +15455,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -15707,7 +15463,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -15948,11 +15704,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -15960,7 +15712,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16201,11 +15953,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -16213,7 +15961,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16454,11 +16202,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -16466,7 +16210,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16707,11 +16451,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -16719,7 +16459,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -16960,11 +16700,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -16972,7 +16708,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17213,11 +16949,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -17225,7 +16957,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17466,11 +17198,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -17478,7 +17206,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17715,11 +17443,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -17727,7 +17451,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -17964,11 +17688,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001107883</t>
@@ -17976,7 +17696,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DEBORA ARANGO PEREZ (IED)</t>
+          <t>DEBORA ARANGO PEREZ</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
